--- a/Analysed/GPT/Combined_Analysis_Summary_gpt5.4Thinking.xlsx
+++ b/Analysed/GPT/Combined_Analysis_Summary_gpt5.4Thinking.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.7179 ± 1.5599</t>
+          <t>1.9575 ± 1.5319</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.0940 ± 1.8543</t>
+          <t>2.4254 ± 1.8813</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6670 ± 0.2444</t>
+          <t>0.6200 ± 0.2462</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,20 +819,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>132</v>
       </c>
       <c r="D14" t="n">
-        <v>1.72625</v>
+        <v>2.187651515151515</v>
       </c>
       <c r="E14" t="n">
-        <v>2.207296989532673</v>
+        <v>2.851763542622407</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3924050632911392</v>
+        <v>0.7251908396946565</v>
       </c>
     </row>
     <row r="15">
@@ -843,19 +843,115 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>83</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4.405869852438506</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2560975609756098</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>58</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.041724137931034</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.4567528553287</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>51</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.355294117647059</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.626578268250593</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>80</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.72625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.207296989532673</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3924050632911392</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>53</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D19" t="n">
         <v>5.548490566037736</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>6.887354148714246</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F19" t="n">
         <v>0.3076923076923077</v>
       </c>
     </row>
